--- a/Assets/GameResource/Excel/触发内容配置.xlsx
+++ b/Assets/GameResource/Excel/触发内容配置.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Game\Assets\GameResource\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5408A9B-9AA3-42E2-B2BD-43CDDD559C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32221A88-8542-4346-BBEE-5B0E702577D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RoomConfigInfo" sheetId="1" r:id="rId1"/>
+    <sheet name="TriggerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
   <si>
     <t>房间id</t>
   </si>
@@ -33,21 +33,9 @@
     <t>自用名称</t>
   </si>
   <si>
-    <t>房间类型</t>
-  </si>
-  <si>
-    <t>房间怪物list</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
-    <t>RoomType</t>
-  </si>
-  <si>
-    <t>MonsterList</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -114,33 +102,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CardDrop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PerkDrop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BagDrop</t>
-  </si>
-  <si>
-    <t>卡牌掉落组id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>建筑掉落组id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>辎重掉落组id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RoomId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -154,6 +119,38 @@
   </si>
   <si>
     <t>宝物3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资组id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件组id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EventId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>房间敌人list</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -501,64 +498,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" customWidth="1"/>
     <col min="4" max="4" width="14.88671875" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.44140625" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -566,388 +556,274 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D12" s="3">
         <v>9008</v>
       </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13">
-        <v>3</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D14" s="3">
         <v>29010</v>
       </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
-      <c r="F14">
-        <v>3</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3">
         <v>39011</v>
       </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-      <c r="F15">
-        <v>3</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B28" s="2"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" s="2"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">

--- a/Assets/GameResource/Excel/触发内容配置.xlsx
+++ b/Assets/GameResource/Excel/触发内容配置.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32221A88-8542-4346-BBEE-5B0E702577D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8310E254-8F4D-47F5-946E-B4B9C91BE0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-12750" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TriggerInfo" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
-  <si>
-    <t>房间id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
   <si>
     <t>自用名称</t>
   </si>
@@ -42,27 +39,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>临时配置</t>
-  </si>
-  <si>
-    <t>小怪</t>
-  </si>
-  <si>
-    <t>精英</t>
-  </si>
-  <si>
-    <t>首领</t>
-  </si>
-  <si>
-    <t>休息</t>
-  </si>
-  <si>
-    <t>商店</t>
-  </si>
-  <si>
-    <t>宝物</t>
-  </si>
-  <si>
     <t>事件</t>
   </si>
   <si>
@@ -106,22 +82,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RoomId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝物1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝物2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝物3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TriggerType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -130,27 +90,123 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>物资组id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事件组id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EventId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MaterialId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemyList</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>房间敌人list</t>
+    <t>触发id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemySet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SupplyId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拾取物资id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扎营点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首领敌人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精英敌人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通敌人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瞭望塔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募单位id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecruitId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遭遇敌人组合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野外招募1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招募</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野外招募2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野外招募3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -158,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,15 +224,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -203,12 +250,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -498,342 +541,406 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.44140625" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
       <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
       <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
       <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
       <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
       <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
       <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="3">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1">
         <v>9008</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
       <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
       <c r="C14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="3">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1">
         <v>29010</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
       <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="3">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1">
         <v>39011</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>25</v>
       </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="2"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="1"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="2"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="D4:D13" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>